--- a/public/data/urunler.xlsx
+++ b/public/data/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuzeypet-my.sharepoint.com/personal/emrahtasdelen_kuzeypet_com/Documents/Masaüstü/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="172" documentId="11_2FAAD7606E74DB0EF18072EE1A4D1940BBBC3A54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D492842F-47DF-44A5-97BD-01A008042414}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_2FAAD7606E74DB0EF18072EE1A4D1940BBBC3A54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1FA9853-7508-4554-90CC-2A0F94AC5871}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -6310,7 +6310,7 @@
         <v>1235</v>
       </c>
       <c r="B91" s="5">
-        <v>12515747</v>
+        <v>12762858</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>1237</v>

--- a/public/data/urunler.xlsx
+++ b/public/data/urunler.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://kuzeypet-my.sharepoint.com/personal/emrahtasdelen_kuzeypet_com/Documents/Masaüstü/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_2FAAD7606E74DB0EF18072EE1A4D1940BBBC3A54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1FA9853-7508-4554-90CC-2A0F94AC5871}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_2FAAD7606E74DB0EF18072EE1A4D1940BBBC3A54" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{542E916B-5A17-4520-A36A-B38C78E791B1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3944" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1459">
   <si>
     <t>Ürün Hiyerarşi 2</t>
   </si>
@@ -4377,6 +4377,42 @@
   </si>
   <si>
     <t>BARK - TOAST - SESLİ REÇEL EKMEK - PELUŞ - XS/M</t>
+  </si>
+  <si>
+    <t>ME-0</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | TUNA MEDLEY - TON BALIĞI 4 ÇEŞİT MİX PAKET - 15G X 100</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | KATSUO AROMALI (ÇİZGİLİ ORKİNOS) KREM KEDİ ÖDÜLÜ 15G X 4</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | MAGURO AROMALI (SARI KANAT ORKİNOS) KREM KEDİ ÖDÜLÜ 15G X 4</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | BONİTO AROMALI (TÜTSÜLENMİŞ TON BALIĞI) KREM KEDİ ÖDÜLÜ 15G X 4</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | SOMON AROMALI KREM KEDİ ÖDÜLÜ 15G X 4</t>
+  </si>
+  <si>
+    <t>ME-O DELİTE | KEÇİ SÜTLÜ TAVUKLU MUS YAVRU KEDİ KONSERVE 80G X 24</t>
+  </si>
+  <si>
+    <t>ME-O CREAMY | YENGEÇ VE TON BALIKLI KEDİ KREM ÖDÜLÜ 15G X 4</t>
+  </si>
+  <si>
+    <t>ME-O | JÖLE İÇERİSİNDE TON BALIKLI KONSERVE 400G X 24</t>
+  </si>
+  <si>
+    <t>ME-O | JÖLE İÇERİSİNDE SARDALYALI KARİDESLİ KONSERVE 400G X 24</t>
+  </si>
+  <si>
+    <t>ME-O | JÖLE İÇERİSİNDE DENİZ LEZZETLERİ KARİDESLİ KONSERVE 400G X 24</t>
+  </si>
+  <si>
+    <t>ME-O DELİT | SOS İÇİNDE TON BALIKLI TAVUKLU POUCH YAŞ MAMA 70G X 12</t>
   </si>
 </sst>
 </file>
@@ -31965,6 +32001,221 @@
         <v>1370</v>
       </c>
     </row>
+    <row r="1398" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1398" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1398" s="5">
+        <v>8850477028944</v>
+      </c>
+      <c r="C1398" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D1398" s="3">
+        <v>3333.33</v>
+      </c>
+      <c r="E1398" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1399" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1399" s="5">
+        <v>8850477018617</v>
+      </c>
+      <c r="C1399" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="D1399" s="3">
+        <v>153.47</v>
+      </c>
+      <c r="E1399" s="4">
+        <v>1920</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1400" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1400" s="5">
+        <v>8850477018600</v>
+      </c>
+      <c r="C1400" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="D1400" s="3">
+        <v>153.47</v>
+      </c>
+      <c r="E1400" s="4">
+        <v>4320</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1401" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1401" s="5">
+        <v>8850477013704</v>
+      </c>
+      <c r="C1401" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D1401" s="3">
+        <v>153.47</v>
+      </c>
+      <c r="E1401" s="4">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1402" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1402" s="5">
+        <v>8850477013698</v>
+      </c>
+      <c r="C1402" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D1402" s="3">
+        <v>153.47</v>
+      </c>
+      <c r="E1402" s="4">
+        <v>15720</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1403" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1403" s="5">
+        <v>8850477024205</v>
+      </c>
+      <c r="C1403" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D1403" s="3">
+        <v>2248.89</v>
+      </c>
+      <c r="E1403" s="4">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1404" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1404" s="5">
+        <v>8850477013711</v>
+      </c>
+      <c r="C1404" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D1404" s="3">
+        <v>153.47</v>
+      </c>
+      <c r="E1404" s="4">
+        <v>15696</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1405" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1405" s="5">
+        <v>18850477002118</v>
+      </c>
+      <c r="C1405" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="D1405" s="3">
+        <v>4013.33</v>
+      </c>
+      <c r="E1405" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1406" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1406" s="5">
+        <v>18850477002101</v>
+      </c>
+      <c r="C1406" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="D1406" s="3">
+        <v>4013.33</v>
+      </c>
+      <c r="E1406" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1407" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1407" s="5">
+        <v>18850477002095</v>
+      </c>
+      <c r="C1407" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D1407" s="3">
+        <v>4013.33</v>
+      </c>
+      <c r="E1407" s="4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1408" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1408" s="5">
+        <v>8850477026346</v>
+      </c>
+      <c r="C1408" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D1408" s="3">
+        <v>888.89</v>
+      </c>
+      <c r="E1408" s="4">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1409" s="2"/>
+      <c r="B1409" s="5"/>
+      <c r="C1409" s="2"/>
+      <c r="D1409" s="3"/>
+      <c r="E1409" s="4"/>
+    </row>
+    <row r="1410" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1410" s="2"/>
+      <c r="B1410" s="5"/>
+      <c r="C1410" s="2"/>
+      <c r="D1410" s="3"/>
+      <c r="E1410" s="4"/>
+    </row>
+    <row r="1411" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1411" s="2"/>
+      <c r="B1411" s="5"/>
+      <c r="C1411" s="2"/>
+      <c r="D1411" s="3"/>
+      <c r="E1411" s="4"/>
+    </row>
+    <row r="1412" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1412" s="2"/>
+      <c r="B1412" s="5"/>
+      <c r="C1412" s="2"/>
+      <c r="D1412" s="3"/>
+      <c r="E1412" s="4"/>
+    </row>
     <row r="1612" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1613" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="1614" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
